--- a/uat-test-plans-reduced30/G2-16151-pdp-be-foundation.xlsx
+++ b/uat-test-plans-reduced30/G2-16151-pdp-be-foundation.xlsx
@@ -597,7 +597,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>[Reduced ~17% — 5/6 checks retained, lowest-priority sections dropped] 2 BE stories (G2-16715, G2-17313) with observable PDP outcomes mapped to 6 outcome-based checklist checks. All 5 evaluation/spike tickets excluded. UAT verifies end-user observable results of the BE API foundation.</t>
+          <t>[Reduced V2 ~17% — 5/6 checks retained; AC and core-case coverage guardrails enforced] 2 BE stories (G2-16715, G2-17313) with observable PDP outcomes mapped to 6 outcome-based checklist checks. All 5 evaluation/spike tickets excluded. UAT verifies end-user observable results of the BE API foundation.</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>payload_bytes=11254; payload_chars=11180; est_tokens~2795; checklist_rows=5; matrix_rows=5; exploratory_rows=4</t>
+          <t>payload_bytes=11886; payload_chars=11810; est_tokens~2953; checklist_rows=5; matrix_rows=6; exploratory_rows=4</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
     <row r="5" ht="64" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>UAT-004</t>
+          <t>UAT-005</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -885,61 +885,62 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Stock &amp; Sizes</t>
+          <t>Product Images</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>PDP correctly reflects overall stock availability status</t>
+          <t>PDP displays product images without broken image states</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>1. Navigate to a product that is in stock and one that is out of stock.
-2. Verify the stock status is reflected correctly on each PDP.</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>In-stock products allow size selection and add-to-bag action.
-Out-of-stock products display an appropriate unavailability indicator.</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-    </row>
-    <row r="6" ht="64" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>UAT-005</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Kozlova, Nika || External</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Product Images</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>PDP displays product images without broken image states</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to a product detail page.
 2. Verify that product images load correctly for at least two shot types (e.g.
 3. front-on and back).</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Product images load without broken image placeholders.
 At least two image shot types are displayed (e.g. 'in' and 'ou' shots).</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr"/>
+      <c r="H5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6" ht="94" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>UAT-006</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Kozlova, Nika || External</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Product Images</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Product images load from the expected image host domain</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>1. Inspect the image URLs on a NAP PDP and an MRP PDP.
+2. Verify the domain matches the expected host (www.net-a-porter.com for NAP, www.mrporter.com for MRP).</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>NAP product images are served from www.net-a-porter.com.
+MRP product images are served from www.mrporter.com.
+No images are served from unexpected or placeholder domains.</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr"/>
@@ -956,7 +957,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1224,7 +1225,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>UAT-003, UAT-004</t>
+          <t>UAT-003</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -1281,7 +1282,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>UAT-005</t>
+          <t>UAT-005, UAT-006</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -1307,6 +1308,63 @@
       <c r="K6" s="5" t="inlineStr">
         <is>
           <t>Security issue flagged in Jira comment (Tapir side) — verify fix status before UAT. Width and quality are hardcoded until Akamai IM is implemented.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="64" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>COV-006</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>G2-17313</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>AC2</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Image URLs use correct domain per brand (NAP vs MRP)</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>UAT-006</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>PR #6479 'add porter image host' and #6423 'brand based solution' directly address domain-per-brand logic</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>Image URL format uses imagesphere pattern; will change when Akamai IM is formalised — test plan may need updating post-Akamai implementation</t>
         </is>
       </c>
     </row>

--- a/uat-test-plans-reduced30/G2-16151-pdp-be-foundation.xlsx
+++ b/uat-test-plans-reduced30/G2-16151-pdp-be-foundation.xlsx
@@ -597,7 +597,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>[Reduced V2 ~17% — 5/6 checks retained; AC and core-case coverage guardrails enforced] 2 BE stories (G2-16715, G2-17313) with observable PDP outcomes mapped to 6 outcome-based checklist checks. All 5 evaluation/spike tickets excluded. UAT verifies end-user observable results of the BE API foundation.</t>
+          <t>[Reduced V2 ~17% — 5/6 checks retained; AC coverage guardrail enforced] 2 BE stories (G2-16715, G2-17313) with observable PDP outcomes mapped to 6 outcome-based checklist checks. All 5 evaluation/spike tickets excluded. UAT verifies end-user observable results of the BE API foundation.</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>payload_bytes=11886; payload_chars=11810; est_tokens~2953; checklist_rows=5; matrix_rows=6; exploratory_rows=4</t>
+          <t>payload_bytes=11871; payload_chars=11795; est_tokens~2949; checklist_rows=5; matrix_rows=6; exploratory_rows=4</t>
         </is>
       </c>
     </row>
